--- a/переводы-13.5/09 Titanic.xlsx
+++ b/переводы-13.5/09 Titanic.xlsx
@@ -4658,7 +4658,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Ой, перестань, мама. У тебя опять пойдёт кровь носом.</t>
+          <t>Ой, перестань, мама. У тебя опять пойдёт кровь из носа.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Союз с Хокли — безупречная партия. Он обеспечит нам выживание.</t>
+          <t>Брак с Хокли — блестящая партия. Он обеспечит нам выживание.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
